--- a/UTCUTS/A1_Outputs/A-O_Fleet.xlsx
+++ b/UTCUTS/A1_Outputs/A-O_Fleet.xlsx
@@ -931,7 +931,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5A599B6-8AF4-4822-929F-D437D65AB770}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05936D0F-F78D-45C0-947D-A6F03551300E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
